--- a/ig/DM-JUIN-2026/ValueSet-jdv-j340-type-act-de-soin-amf-finess.xlsx
+++ b/ig/DM-JUIN-2026/ValueSet-jdv-j340-type-act-de-soin-amf-finess.xlsx
@@ -108,7 +108,7 @@
     <t>=</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r374-nature-activite-smsse-regulee#AS</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r374-nature-activite-smsse-regulee|AS</t>
   </si>
   <si>
     <t/>
